--- a/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
@@ -488,14 +488,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Первичная проверка и маршрутизация</t>
+          <t>Детальная проверка — по желанию</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ответьте на каждый вопрос: Да / Нет / Не знаю. Итог и следующий шаг считаются автоматически. Жёлтые ячейки — ввод.</t>
+          <t>Необязательно. Ситуация выбирается в файле 01, таблица 1. Эта проверка — для случая, когда вы сомневаетесь в выборе: ответьте на вопросы Да / Нет / Не знаю, итог покажет ситуацию или границу. Строку «Последний день срока оплаты» ниже заполняйте в любом случае (шаг 6). Жёлтые ячейки — ввод.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Нет → шаги 2–5</t>
+          <t>Нет → шаги 2–5 (ситуация Г)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Да → шаг 5</t>
+          <t>Да → шаг 5 (ситуация Д)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Нет → шаг 6</t>
+          <t>Нет → шаг 6 (ситуация Б)</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Нет → шаг 4</t>
+          <t>Нет → шаг 4 (ситуация Е)</t>
         </is>
       </c>
     </row>
@@ -5100,12 +5100,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Ответьте на все вопросы</t>
+          <t>Проверка не пройдена</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Заполните колонку «Ответ» во всех строках.</t>
+          <t>Проверка по желанию. Для итога ответьте на все вопросы; без неё выберите ситуацию в файле 01, таблица 1.</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ШАГИ 2–5: оформить и сдать работы</t>
+          <t>СИТУАЦИЯ Г, ШАГ 2: оформить и сдать работы</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Оформите акты (файлы 04–07), проверьте (09), передайте с доказательством и закройте замечания (10).</t>
+          <t>Оформите акты (файлы 04–07), проверьте (09), передайте с доказательством и закройте замечания (10), затем шаг 6.</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Доведите до конца шаги 2–5 и сверку (шаг 6). Вернитесь к маршруту на следующий день после истечения срока.</t>
+          <t>Маршрут начните на следующий день после срока. До этого документы можно готовить по ситуации Г (шаги 2–5).</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ШАГ 4: подтвердить передачу</t>
+          <t>СИТУАЦИЯ Е, ШАГ 4: подтвердить передачу</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ШАГ 5: закрыть замечания</t>
+          <t>СИТУАЦИЯ Д, ШАГ 5: закрыть замечания</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ШАГ 6: подтвердить сумму</t>
+          <t>СИТУАЦИЯ Б, ШАГ 6: подтвердить сумму</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Заполните реестр взаиморасчётов (файл 08) и предложите заказчику акт сверки.</t>
+          <t>Заполните реестр взаиморасчётов (файл 08) и предложите заказчику акт сверки; шаги 2–5 не нужны.</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Шаг 6 → шаг 7: зафиксируйте долг и дату начала просрочки, затем переговоры (файл 11).</t>
+          <t>Ситуация А: шаги 6–12. Зафиксируйте долг и дату начала просрочки, затем переговоры (файл 11).</t>
         </is>
       </c>
     </row>

--- a/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
@@ -549,7 +549,7 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Нет → шаги 2–5 (ситуация Г)</t>
+          <t>Нет → ситуация Г, Д или Е (шаги 2–5), затем проверка G</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Нет → шаг 4 (ситуация Е)</t>
+          <t>Нет → шаг 4 (ситуация Г)</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <f>IF(COUNTA(C5:C20)&lt;16,"НЕ ЗАПОЛНЕНО",IF(C13="Да","B3",IF(C13="Не знаю","ПРОВЕРКА B3",IF(OR(C7="Да",C8="Да",C9="Да",C10="Да"),"B4",IF(C12="Да","B2",IF(C14="Да","B1",IF(C5&lt;&gt;"Да","НЕ ПРИМЕНИМО",IF(C6&lt;&gt;"Да","ДОКУМЕНТЫ",IF(C15&lt;&gt;"Да","РАНО-СРОК",IF(C16&lt;&gt;"Да","РАНО",IF(C20&lt;&gt;"Да","ПЕРЕДАЧА",IF(C11="Да","ЗАМЕЧАНИЯ",IF(C19&lt;&gt;"Да","СВЕРКА","OK")))))))))))))</f>
+        <f>IF(COUNTA(C5:C20)&lt;16,"НЕ ЗАПОЛНЕНО",IF(C13="Да","B3",IF(C13="Не знаю","ПРОВЕРКА B3",IF(OR(C7="Да",C8="Да",C9="Да",C10="Да"),"B4",IF(C12="Да","B2",IF(C14="Да","B1",IF(C5&lt;&gt;"Да","НЕ ПРИМЕНИМО",IF(C6&lt;&gt;"Да",IF(C20&lt;&gt;"Да","ДОКУМЕНТЫ",IF(C11="Да","ЗАМЕЧАНИЯ","ПОДПИСЬ")),IF(C15&lt;&gt;"Да","РАНО-СРОК",IF(C16&lt;&gt;"Да","РАНО",IF(C20&lt;&gt;"Да","ПЕРЕДАЧА",IF(C11="Да","ЗАМЕЧАНИЯ",IF(C19&lt;&gt;"Да","СВЕРКА","OK")))))))))))))</f>
         <v/>
       </c>
     </row>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C23" s="7">
-        <f>VLOOKUP(C22,Справочник!$A$2:$C$15,2,FALSE)</f>
+        <f>VLOOKUP(C22,Справочник!$A$2:$C$16,2,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <f>VLOOKUP(C22,Справочник!$A$2:$C$15,3,FALSE)</f>
+        <f>VLOOKUP(C22,Справочник!$A$2:$C$16,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="4">
-        <f>IF(F5="","",IFERROR(VLOOKUP(F5,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F5="","",IFERROR(VLOOKUP(F5,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="4">
-        <f>IF(F6="","",IFERROR(VLOOKUP(F6,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F6="","",IFERROR(VLOOKUP(F6,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="4">
-        <f>IF(F7="","",IFERROR(VLOOKUP(F7,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F7="","",IFERROR(VLOOKUP(F7,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="4">
-        <f>IF(F8="","",IFERROR(VLOOKUP(F8,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F8="","",IFERROR(VLOOKUP(F8,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="4">
-        <f>IF(F9="","",IFERROR(VLOOKUP(F9,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F9="","",IFERROR(VLOOKUP(F9,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="4">
-        <f>IF(F10="","",IFERROR(VLOOKUP(F10,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F10="","",IFERROR(VLOOKUP(F10,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="4">
-        <f>IF(F11="","",IFERROR(VLOOKUP(F11,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F11="","",IFERROR(VLOOKUP(F11,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="4">
-        <f>IF(F12="","",IFERROR(VLOOKUP(F12,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F12="","",IFERROR(VLOOKUP(F12,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="4">
-        <f>IF(F13="","",IFERROR(VLOOKUP(F13,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F13="","",IFERROR(VLOOKUP(F13,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="4">
-        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="4">
-        <f>IF(F15="","",IFERROR(VLOOKUP(F15,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F15="","",IFERROR(VLOOKUP(F15,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="4">
-        <f>IF(F16="","",IFERROR(VLOOKUP(F16,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F16="","",IFERROR(VLOOKUP(F16,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="4">
-        <f>IF(F17="","",IFERROR(VLOOKUP(F17,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F17="","",IFERROR(VLOOKUP(F17,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="4">
-        <f>IF(F18="","",IFERROR(VLOOKUP(F18,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F18="","",IFERROR(VLOOKUP(F18,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n"/>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="4">
-        <f>IF(F19="","",IFERROR(VLOOKUP(F19,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F19="","",IFERROR(VLOOKUP(F19,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n"/>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="4">
-        <f>IF(F20="","",IFERROR(VLOOKUP(F20,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F20="","",IFERROR(VLOOKUP(F20,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="4">
-        <f>IF(F21="","",IFERROR(VLOOKUP(F21,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F21="","",IFERROR(VLOOKUP(F21,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="4">
-        <f>IF(F22="","",IFERROR(VLOOKUP(F22,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F22="","",IFERROR(VLOOKUP(F22,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H22" s="10" t="n"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="4">
-        <f>IF(F23="","",IFERROR(VLOOKUP(F23,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F23="","",IFERROR(VLOOKUP(F23,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H23" s="10" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="4">
-        <f>IF(F24="","",IFERROR(VLOOKUP(F24,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F24="","",IFERROR(VLOOKUP(F24,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H24" s="10" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="4">
-        <f>IF(F25="","",IFERROR(VLOOKUP(F25,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F25="","",IFERROR(VLOOKUP(F25,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H25" s="10" t="n"/>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="4">
-        <f>IF(F26="","",IFERROR(VLOOKUP(F26,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F26="","",IFERROR(VLOOKUP(F26,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H26" s="10" t="n"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="4">
-        <f>IF(F27="","",IFERROR(VLOOKUP(F27,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F27="","",IFERROR(VLOOKUP(F27,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H27" s="10" t="n"/>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="4">
-        <f>IF(F28="","",IFERROR(VLOOKUP(F28,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F28="","",IFERROR(VLOOKUP(F28,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H28" s="10" t="n"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="4">
-        <f>IF(F29="","",IFERROR(VLOOKUP(F29,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F29="","",IFERROR(VLOOKUP(F29,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H29" s="10" t="n"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="4">
-        <f>IF(F30="","",IFERROR(VLOOKUP(F30,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F30="","",IFERROR(VLOOKUP(F30,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H30" s="10" t="n"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="4">
-        <f>IF(F31="","",IFERROR(VLOOKUP(F31,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F31="","",IFERROR(VLOOKUP(F31,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H31" s="10" t="n"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="4">
-        <f>IF(F32="","",IFERROR(VLOOKUP(F32,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F32="","",IFERROR(VLOOKUP(F32,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H32" s="10" t="n"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="4">
-        <f>IF(F33="","",IFERROR(VLOOKUP(F33,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F33="","",IFERROR(VLOOKUP(F33,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H33" s="10" t="n"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="4">
-        <f>IF(F34="","",IFERROR(VLOOKUP(F34,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F34="","",IFERROR(VLOOKUP(F34,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H34" s="10" t="n"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="4">
-        <f>IF(F35="","",IFERROR(VLOOKUP(F35,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F35="","",IFERROR(VLOOKUP(F35,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H35" s="10" t="n"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="4">
-        <f>IF(F36="","",IFERROR(VLOOKUP(F36,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F36="","",IFERROR(VLOOKUP(F36,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H36" s="10" t="n"/>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="4">
-        <f>IF(F37="","",IFERROR(VLOOKUP(F37,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F37="","",IFERROR(VLOOKUP(F37,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H37" s="10" t="n"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="4">
-        <f>IF(F38="","",IFERROR(VLOOKUP(F38,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F38="","",IFERROR(VLOOKUP(F38,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H38" s="10" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="4">
-        <f>IF(F39="","",IFERROR(VLOOKUP(F39,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F39="","",IFERROR(VLOOKUP(F39,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H39" s="10" t="n"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="4">
-        <f>IF(F40="","",IFERROR(VLOOKUP(F40,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F40="","",IFERROR(VLOOKUP(F40,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H40" s="10" t="n"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="4">
-        <f>IF(F41="","",IFERROR(VLOOKUP(F41,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F41="","",IFERROR(VLOOKUP(F41,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H41" s="10" t="n"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="4">
-        <f>IF(F42="","",IFERROR(VLOOKUP(F42,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F42="","",IFERROR(VLOOKUP(F42,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H42" s="10" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="4">
-        <f>IF(F43="","",IFERROR(VLOOKUP(F43,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F43="","",IFERROR(VLOOKUP(F43,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H43" s="10" t="n"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="4">
-        <f>IF(F44="","",IFERROR(VLOOKUP(F44,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F44="","",IFERROR(VLOOKUP(F44,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H44" s="10" t="n"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="F45" s="5" t="n"/>
       <c r="G45" s="4">
-        <f>IF(F45="","",IFERROR(VLOOKUP(F45,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F45="","",IFERROR(VLOOKUP(F45,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H45" s="10" t="n"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F46" s="5" t="n"/>
       <c r="G46" s="4">
-        <f>IF(F46="","",IFERROR(VLOOKUP(F46,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F46="","",IFERROR(VLOOKUP(F46,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H46" s="10" t="n"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F47" s="5" t="n"/>
       <c r="G47" s="4">
-        <f>IF(F47="","",IFERROR(VLOOKUP(F47,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F47="","",IFERROR(VLOOKUP(F47,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H47" s="10" t="n"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F48" s="5" t="n"/>
       <c r="G48" s="4">
-        <f>IF(F48="","",IFERROR(VLOOKUP(F48,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F48="","",IFERROR(VLOOKUP(F48,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H48" s="10" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="4">
-        <f>IF(F49="","",IFERROR(VLOOKUP(F49,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F49="","",IFERROR(VLOOKUP(F49,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H49" s="10" t="n"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F50" s="5" t="n"/>
       <c r="G50" s="4">
-        <f>IF(F50="","",IFERROR(VLOOKUP(F50,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F50="","",IFERROR(VLOOKUP(F50,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H50" s="10" t="n"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F51" s="5" t="n"/>
       <c r="G51" s="4">
-        <f>IF(F51="","",IFERROR(VLOOKUP(F51,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F51="","",IFERROR(VLOOKUP(F51,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H51" s="10" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F52" s="5" t="n"/>
       <c r="G52" s="4">
-        <f>IF(F52="","",IFERROR(VLOOKUP(F52,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F52="","",IFERROR(VLOOKUP(F52,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H52" s="10" t="n"/>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F53" s="5" t="n"/>
       <c r="G53" s="4">
-        <f>IF(F53="","",IFERROR(VLOOKUP(F53,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F53="","",IFERROR(VLOOKUP(F53,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H53" s="10" t="n"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="4">
-        <f>IF(F54="","",IFERROR(VLOOKUP(F54,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F54="","",IFERROR(VLOOKUP(F54,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H54" s="10" t="n"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="4">
-        <f>IF(F55="","",IFERROR(VLOOKUP(F55,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F55="","",IFERROR(VLOOKUP(F55,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H55" s="10" t="n"/>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="4">
-        <f>IF(F56="","",IFERROR(VLOOKUP(F56,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F56="","",IFERROR(VLOOKUP(F56,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H56" s="10" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F57" s="5" t="n"/>
       <c r="G57" s="4">
-        <f>IF(F57="","",IFERROR(VLOOKUP(F57,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F57="","",IFERROR(VLOOKUP(F57,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H57" s="10" t="n"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F58" s="5" t="n"/>
       <c r="G58" s="4">
-        <f>IF(F58="","",IFERROR(VLOOKUP(F58,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F58="","",IFERROR(VLOOKUP(F58,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H58" s="10" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F59" s="5" t="n"/>
       <c r="G59" s="4">
-        <f>IF(F59="","",IFERROR(VLOOKUP(F59,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F59="","",IFERROR(VLOOKUP(F59,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H59" s="10" t="n"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F60" s="5" t="n"/>
       <c r="G60" s="4">
-        <f>IF(F60="","",IFERROR(VLOOKUP(F60,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F60="","",IFERROR(VLOOKUP(F60,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H60" s="10" t="n"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F61" s="5" t="n"/>
       <c r="G61" s="4">
-        <f>IF(F61="","",IFERROR(VLOOKUP(F61,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F61="","",IFERROR(VLOOKUP(F61,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H61" s="10" t="n"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F62" s="5" t="n"/>
       <c r="G62" s="4">
-        <f>IF(F62="","",IFERROR(VLOOKUP(F62,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F62="","",IFERROR(VLOOKUP(F62,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H62" s="10" t="n"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F63" s="5" t="n"/>
       <c r="G63" s="4">
-        <f>IF(F63="","",IFERROR(VLOOKUP(F63,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F63="","",IFERROR(VLOOKUP(F63,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H63" s="10" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F64" s="5" t="n"/>
       <c r="G64" s="4">
-        <f>IF(F64="","",IFERROR(VLOOKUP(F64,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F64="","",IFERROR(VLOOKUP(F64,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H64" s="10" t="n"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F65" s="5" t="n"/>
       <c r="G65" s="4">
-        <f>IF(F65="","",IFERROR(VLOOKUP(F65,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F65="","",IFERROR(VLOOKUP(F65,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H65" s="10" t="n"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F66" s="5" t="n"/>
       <c r="G66" s="4">
-        <f>IF(F66="","",IFERROR(VLOOKUP(F66,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F66="","",IFERROR(VLOOKUP(F66,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H66" s="10" t="n"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F67" s="5" t="n"/>
       <c r="G67" s="4">
-        <f>IF(F67="","",IFERROR(VLOOKUP(F67,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F67="","",IFERROR(VLOOKUP(F67,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H67" s="10" t="n"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F68" s="5" t="n"/>
       <c r="G68" s="4">
-        <f>IF(F68="","",IFERROR(VLOOKUP(F68,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F68="","",IFERROR(VLOOKUP(F68,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H68" s="10" t="n"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F69" s="5" t="n"/>
       <c r="G69" s="4">
-        <f>IF(F69="","",IFERROR(VLOOKUP(F69,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F69="","",IFERROR(VLOOKUP(F69,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H69" s="10" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F70" s="5" t="n"/>
       <c r="G70" s="4">
-        <f>IF(F70="","",IFERROR(VLOOKUP(F70,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F70="","",IFERROR(VLOOKUP(F70,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H70" s="10" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F71" s="5" t="n"/>
       <c r="G71" s="4">
-        <f>IF(F71="","",IFERROR(VLOOKUP(F71,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F71="","",IFERROR(VLOOKUP(F71,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H71" s="10" t="n"/>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F72" s="5" t="n"/>
       <c r="G72" s="4">
-        <f>IF(F72="","",IFERROR(VLOOKUP(F72,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F72="","",IFERROR(VLOOKUP(F72,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H72" s="10" t="n"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="F73" s="5" t="n"/>
       <c r="G73" s="4">
-        <f>IF(F73="","",IFERROR(VLOOKUP(F73,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F73="","",IFERROR(VLOOKUP(F73,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H73" s="10" t="n"/>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="F74" s="5" t="n"/>
       <c r="G74" s="4">
-        <f>IF(F74="","",IFERROR(VLOOKUP(F74,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F74="","",IFERROR(VLOOKUP(F74,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H74" s="10" t="n"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="F75" s="5" t="n"/>
       <c r="G75" s="4">
-        <f>IF(F75="","",IFERROR(VLOOKUP(F75,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F75="","",IFERROR(VLOOKUP(F75,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H75" s="10" t="n"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F76" s="5" t="n"/>
       <c r="G76" s="4">
-        <f>IF(F76="","",IFERROR(VLOOKUP(F76,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F76="","",IFERROR(VLOOKUP(F76,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H76" s="10" t="n"/>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F77" s="5" t="n"/>
       <c r="G77" s="4">
-        <f>IF(F77="","",IFERROR(VLOOKUP(F77,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F77="","",IFERROR(VLOOKUP(F77,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H77" s="10" t="n"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F78" s="5" t="n"/>
       <c r="G78" s="4">
-        <f>IF(F78="","",IFERROR(VLOOKUP(F78,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F78="","",IFERROR(VLOOKUP(F78,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H78" s="10" t="n"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F79" s="5" t="n"/>
       <c r="G79" s="4">
-        <f>IF(F79="","",IFERROR(VLOOKUP(F79,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F79="","",IFERROR(VLOOKUP(F79,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H79" s="10" t="n"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="F80" s="5" t="n"/>
       <c r="G80" s="4">
-        <f>IF(F80="","",IFERROR(VLOOKUP(F80,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F80="","",IFERROR(VLOOKUP(F80,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H80" s="10" t="n"/>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="F81" s="5" t="n"/>
       <c r="G81" s="4">
-        <f>IF(F81="","",IFERROR(VLOOKUP(F81,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F81="","",IFERROR(VLOOKUP(F81,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H81" s="10" t="n"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="F82" s="5" t="n"/>
       <c r="G82" s="4">
-        <f>IF(F82="","",IFERROR(VLOOKUP(F82,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F82="","",IFERROR(VLOOKUP(F82,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H82" s="10" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F83" s="5" t="n"/>
       <c r="G83" s="4">
-        <f>IF(F83="","",IFERROR(VLOOKUP(F83,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F83="","",IFERROR(VLOOKUP(F83,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H83" s="10" t="n"/>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="F84" s="5" t="n"/>
       <c r="G84" s="4">
-        <f>IF(F84="","",IFERROR(VLOOKUP(F84,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F84="","",IFERROR(VLOOKUP(F84,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H84" s="10" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F85" s="5" t="n"/>
       <c r="G85" s="4">
-        <f>IF(F85="","",IFERROR(VLOOKUP(F85,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F85="","",IFERROR(VLOOKUP(F85,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H85" s="10" t="n"/>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F86" s="5" t="n"/>
       <c r="G86" s="4">
-        <f>IF(F86="","",IFERROR(VLOOKUP(F86,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F86="","",IFERROR(VLOOKUP(F86,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H86" s="10" t="n"/>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F87" s="5" t="n"/>
       <c r="G87" s="4">
-        <f>IF(F87="","",IFERROR(VLOOKUP(F87,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F87="","",IFERROR(VLOOKUP(F87,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H87" s="10" t="n"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F88" s="5" t="n"/>
       <c r="G88" s="4">
-        <f>IF(F88="","",IFERROR(VLOOKUP(F88,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F88="","",IFERROR(VLOOKUP(F88,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H88" s="10" t="n"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="F89" s="5" t="n"/>
       <c r="G89" s="4">
-        <f>IF(F89="","",IFERROR(VLOOKUP(F89,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F89="","",IFERROR(VLOOKUP(F89,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H89" s="10" t="n"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="4">
-        <f>IF(F90="","",IFERROR(VLOOKUP(F90,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F90="","",IFERROR(VLOOKUP(F90,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H90" s="10" t="n"/>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F91" s="5" t="n"/>
       <c r="G91" s="4">
-        <f>IF(F91="","",IFERROR(VLOOKUP(F91,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F91="","",IFERROR(VLOOKUP(F91,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H91" s="10" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="F92" s="5" t="n"/>
       <c r="G92" s="4">
-        <f>IF(F92="","",IFERROR(VLOOKUP(F92,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F92="","",IFERROR(VLOOKUP(F92,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H92" s="10" t="n"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F93" s="5" t="n"/>
       <c r="G93" s="4">
-        <f>IF(F93="","",IFERROR(VLOOKUP(F93,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F93="","",IFERROR(VLOOKUP(F93,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H93" s="10" t="n"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="F94" s="5" t="n"/>
       <c r="G94" s="4">
-        <f>IF(F94="","",IFERROR(VLOOKUP(F94,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F94="","",IFERROR(VLOOKUP(F94,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H94" s="10" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="F95" s="5" t="n"/>
       <c r="G95" s="4">
-        <f>IF(F95="","",IFERROR(VLOOKUP(F95,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F95="","",IFERROR(VLOOKUP(F95,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H95" s="10" t="n"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="F96" s="5" t="n"/>
       <c r="G96" s="4">
-        <f>IF(F96="","",IFERROR(VLOOKUP(F96,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F96="","",IFERROR(VLOOKUP(F96,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H96" s="10" t="n"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F97" s="5" t="n"/>
       <c r="G97" s="4">
-        <f>IF(F97="","",IFERROR(VLOOKUP(F97,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F97="","",IFERROR(VLOOKUP(F97,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H97" s="10" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F98" s="5" t="n"/>
       <c r="G98" s="4">
-        <f>IF(F98="","",IFERROR(VLOOKUP(F98,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F98="","",IFERROR(VLOOKUP(F98,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H98" s="10" t="n"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F99" s="5" t="n"/>
       <c r="G99" s="4">
-        <f>IF(F99="","",IFERROR(VLOOKUP(F99,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F99="","",IFERROR(VLOOKUP(F99,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H99" s="10" t="n"/>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F100" s="5" t="n"/>
       <c r="G100" s="4">
-        <f>IF(F100="","",IFERROR(VLOOKUP(F100,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F100="","",IFERROR(VLOOKUP(F100,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H100" s="10" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F101" s="5" t="n"/>
       <c r="G101" s="4">
-        <f>IF(F101="","",IFERROR(VLOOKUP(F101,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F101="","",IFERROR(VLOOKUP(F101,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H101" s="10" t="n"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="F102" s="5" t="n"/>
       <c r="G102" s="4">
-        <f>IF(F102="","",IFERROR(VLOOKUP(F102,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F102="","",IFERROR(VLOOKUP(F102,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H102" s="10" t="n"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F103" s="5" t="n"/>
       <c r="G103" s="4">
-        <f>IF(F103="","",IFERROR(VLOOKUP(F103,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F103="","",IFERROR(VLOOKUP(F103,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H103" s="10" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F104" s="5" t="n"/>
       <c r="G104" s="4">
-        <f>IF(F104="","",IFERROR(VLOOKUP(F104,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F104="","",IFERROR(VLOOKUP(F104,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H104" s="10" t="n"/>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F105" s="5" t="n"/>
       <c r="G105" s="4">
-        <f>IF(F105="","",IFERROR(VLOOKUP(F105,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F105="","",IFERROR(VLOOKUP(F105,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H105" s="10" t="n"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F106" s="5" t="n"/>
       <c r="G106" s="4">
-        <f>IF(F106="","",IFERROR(VLOOKUP(F106,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F106="","",IFERROR(VLOOKUP(F106,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H106" s="10" t="n"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F107" s="5" t="n"/>
       <c r="G107" s="4">
-        <f>IF(F107="","",IFERROR(VLOOKUP(F107,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F107="","",IFERROR(VLOOKUP(F107,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H107" s="10" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="4">
-        <f>IF(F108="","",IFERROR(VLOOKUP(F108,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F108="","",IFERROR(VLOOKUP(F108,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H108" s="10" t="n"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F109" s="5" t="n"/>
       <c r="G109" s="4">
-        <f>IF(F109="","",IFERROR(VLOOKUP(F109,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F109="","",IFERROR(VLOOKUP(F109,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H109" s="10" t="n"/>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F110" s="5" t="n"/>
       <c r="G110" s="4">
-        <f>IF(F110="","",IFERROR(VLOOKUP(F110,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F110="","",IFERROR(VLOOKUP(F110,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H110" s="10" t="n"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F111" s="5" t="n"/>
       <c r="G111" s="4">
-        <f>IF(F111="","",IFERROR(VLOOKUP(F111,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F111="","",IFERROR(VLOOKUP(F111,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H111" s="10" t="n"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F112" s="5" t="n"/>
       <c r="G112" s="4">
-        <f>IF(F112="","",IFERROR(VLOOKUP(F112,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F112="","",IFERROR(VLOOKUP(F112,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H112" s="10" t="n"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F113" s="5" t="n"/>
       <c r="G113" s="4">
-        <f>IF(F113="","",IFERROR(VLOOKUP(F113,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F113="","",IFERROR(VLOOKUP(F113,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H113" s="10" t="n"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="F114" s="5" t="n"/>
       <c r="G114" s="4">
-        <f>IF(F114="","",IFERROR(VLOOKUP(F114,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F114="","",IFERROR(VLOOKUP(F114,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H114" s="10" t="n"/>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F115" s="5" t="n"/>
       <c r="G115" s="4">
-        <f>IF(F115="","",IFERROR(VLOOKUP(F115,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F115="","",IFERROR(VLOOKUP(F115,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H115" s="10" t="n"/>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F116" s="5" t="n"/>
       <c r="G116" s="4">
-        <f>IF(F116="","",IFERROR(VLOOKUP(F116,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F116="","",IFERROR(VLOOKUP(F116,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H116" s="10" t="n"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F117" s="5" t="n"/>
       <c r="G117" s="4">
-        <f>IF(F117="","",IFERROR(VLOOKUP(F117,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F117="","",IFERROR(VLOOKUP(F117,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H117" s="10" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F118" s="5" t="n"/>
       <c r="G118" s="4">
-        <f>IF(F118="","",IFERROR(VLOOKUP(F118,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F118="","",IFERROR(VLOOKUP(F118,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H118" s="10" t="n"/>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F119" s="5" t="n"/>
       <c r="G119" s="4">
-        <f>IF(F119="","",IFERROR(VLOOKUP(F119,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F119="","",IFERROR(VLOOKUP(F119,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H119" s="10" t="n"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F120" s="5" t="n"/>
       <c r="G120" s="4">
-        <f>IF(F120="","",IFERROR(VLOOKUP(F120,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F120="","",IFERROR(VLOOKUP(F120,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H120" s="10" t="n"/>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F121" s="5" t="n"/>
       <c r="G121" s="4">
-        <f>IF(F121="","",IFERROR(VLOOKUP(F121,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F121="","",IFERROR(VLOOKUP(F121,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H121" s="10" t="n"/>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="F122" s="5" t="n"/>
       <c r="G122" s="4">
-        <f>IF(F122="","",IFERROR(VLOOKUP(F122,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F122="","",IFERROR(VLOOKUP(F122,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H122" s="10" t="n"/>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F123" s="5" t="n"/>
       <c r="G123" s="4">
-        <f>IF(F123="","",IFERROR(VLOOKUP(F123,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F123="","",IFERROR(VLOOKUP(F123,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H123" s="10" t="n"/>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F124" s="5" t="n"/>
       <c r="G124" s="4">
-        <f>IF(F124="","",IFERROR(VLOOKUP(F124,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F124="","",IFERROR(VLOOKUP(F124,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H124" s="10" t="n"/>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="F125" s="5" t="n"/>
       <c r="G125" s="4">
-        <f>IF(F125="","",IFERROR(VLOOKUP(F125,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F125="","",IFERROR(VLOOKUP(F125,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H125" s="10" t="n"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F126" s="5" t="n"/>
       <c r="G126" s="4">
-        <f>IF(F126="","",IFERROR(VLOOKUP(F126,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F126="","",IFERROR(VLOOKUP(F126,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H126" s="10" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F127" s="5" t="n"/>
       <c r="G127" s="4">
-        <f>IF(F127="","",IFERROR(VLOOKUP(F127,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F127="","",IFERROR(VLOOKUP(F127,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H127" s="10" t="n"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F128" s="5" t="n"/>
       <c r="G128" s="4">
-        <f>IF(F128="","",IFERROR(VLOOKUP(F128,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F128="","",IFERROR(VLOOKUP(F128,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H128" s="10" t="n"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="F129" s="5" t="n"/>
       <c r="G129" s="4">
-        <f>IF(F129="","",IFERROR(VLOOKUP(F129,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F129="","",IFERROR(VLOOKUP(F129,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H129" s="10" t="n"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F130" s="5" t="n"/>
       <c r="G130" s="4">
-        <f>IF(F130="","",IFERROR(VLOOKUP(F130,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F130="","",IFERROR(VLOOKUP(F130,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H130" s="10" t="n"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="F131" s="5" t="n"/>
       <c r="G131" s="4">
-        <f>IF(F131="","",IFERROR(VLOOKUP(F131,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F131="","",IFERROR(VLOOKUP(F131,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H131" s="10" t="n"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F132" s="5" t="n"/>
       <c r="G132" s="4">
-        <f>IF(F132="","",IFERROR(VLOOKUP(F132,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F132="","",IFERROR(VLOOKUP(F132,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H132" s="10" t="n"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="F133" s="5" t="n"/>
       <c r="G133" s="4">
-        <f>IF(F133="","",IFERROR(VLOOKUP(F133,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F133="","",IFERROR(VLOOKUP(F133,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H133" s="10" t="n"/>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F134" s="5" t="n"/>
       <c r="G134" s="4">
-        <f>IF(F134="","",IFERROR(VLOOKUP(F134,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F134="","",IFERROR(VLOOKUP(F134,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H134" s="10" t="n"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="F135" s="5" t="n"/>
       <c r="G135" s="4">
-        <f>IF(F135="","",IFERROR(VLOOKUP(F135,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F135="","",IFERROR(VLOOKUP(F135,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H135" s="10" t="n"/>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="F136" s="5" t="n"/>
       <c r="G136" s="4">
-        <f>IF(F136="","",IFERROR(VLOOKUP(F136,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F136="","",IFERROR(VLOOKUP(F136,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H136" s="10" t="n"/>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F137" s="5" t="n"/>
       <c r="G137" s="4">
-        <f>IF(F137="","",IFERROR(VLOOKUP(F137,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F137="","",IFERROR(VLOOKUP(F137,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H137" s="10" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="F138" s="5" t="n"/>
       <c r="G138" s="4">
-        <f>IF(F138="","",IFERROR(VLOOKUP(F138,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F138="","",IFERROR(VLOOKUP(F138,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H138" s="10" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F139" s="5" t="n"/>
       <c r="G139" s="4">
-        <f>IF(F139="","",IFERROR(VLOOKUP(F139,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F139="","",IFERROR(VLOOKUP(F139,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H139" s="10" t="n"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="F140" s="5" t="n"/>
       <c r="G140" s="4">
-        <f>IF(F140="","",IFERROR(VLOOKUP(F140,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F140="","",IFERROR(VLOOKUP(F140,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H140" s="10" t="n"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="F141" s="5" t="n"/>
       <c r="G141" s="4">
-        <f>IF(F141="","",IFERROR(VLOOKUP(F141,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F141="","",IFERROR(VLOOKUP(F141,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H141" s="10" t="n"/>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="F142" s="5" t="n"/>
       <c r="G142" s="4">
-        <f>IF(F142="","",IFERROR(VLOOKUP(F142,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F142="","",IFERROR(VLOOKUP(F142,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H142" s="10" t="n"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F143" s="5" t="n"/>
       <c r="G143" s="4">
-        <f>IF(F143="","",IFERROR(VLOOKUP(F143,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F143="","",IFERROR(VLOOKUP(F143,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H143" s="10" t="n"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F144" s="5" t="n"/>
       <c r="G144" s="4">
-        <f>IF(F144="","",IFERROR(VLOOKUP(F144,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F144="","",IFERROR(VLOOKUP(F144,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H144" s="10" t="n"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F145" s="5" t="n"/>
       <c r="G145" s="4">
-        <f>IF(F145="","",IFERROR(VLOOKUP(F145,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F145="","",IFERROR(VLOOKUP(F145,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H145" s="10" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F146" s="5" t="n"/>
       <c r="G146" s="4">
-        <f>IF(F146="","",IFERROR(VLOOKUP(F146,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F146="","",IFERROR(VLOOKUP(F146,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H146" s="10" t="n"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="F147" s="5" t="n"/>
       <c r="G147" s="4">
-        <f>IF(F147="","",IFERROR(VLOOKUP(F147,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F147="","",IFERROR(VLOOKUP(F147,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H147" s="10" t="n"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="F148" s="5" t="n"/>
       <c r="G148" s="4">
-        <f>IF(F148="","",IFERROR(VLOOKUP(F148,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F148="","",IFERROR(VLOOKUP(F148,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H148" s="10" t="n"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="F149" s="5" t="n"/>
       <c r="G149" s="4">
-        <f>IF(F149="","",IFERROR(VLOOKUP(F149,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F149="","",IFERROR(VLOOKUP(F149,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H149" s="10" t="n"/>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F150" s="5" t="n"/>
       <c r="G150" s="4">
-        <f>IF(F150="","",IFERROR(VLOOKUP(F150,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F150="","",IFERROR(VLOOKUP(F150,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H150" s="10" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F151" s="5" t="n"/>
       <c r="G151" s="4">
-        <f>IF(F151="","",IFERROR(VLOOKUP(F151,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F151="","",IFERROR(VLOOKUP(F151,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H151" s="10" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F152" s="5" t="n"/>
       <c r="G152" s="4">
-        <f>IF(F152="","",IFERROR(VLOOKUP(F152,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F152="","",IFERROR(VLOOKUP(F152,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H152" s="10" t="n"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F153" s="5" t="n"/>
       <c r="G153" s="4">
-        <f>IF(F153="","",IFERROR(VLOOKUP(F153,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F153="","",IFERROR(VLOOKUP(F153,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H153" s="10" t="n"/>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F154" s="5" t="n"/>
       <c r="G154" s="4">
-        <f>IF(F154="","",IFERROR(VLOOKUP(F154,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F154="","",IFERROR(VLOOKUP(F154,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H154" s="10" t="n"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="F155" s="5" t="n"/>
       <c r="G155" s="4">
-        <f>IF(F155="","",IFERROR(VLOOKUP(F155,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F155="","",IFERROR(VLOOKUP(F155,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H155" s="10" t="n"/>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F156" s="5" t="n"/>
       <c r="G156" s="4">
-        <f>IF(F156="","",IFERROR(VLOOKUP(F156,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F156="","",IFERROR(VLOOKUP(F156,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H156" s="10" t="n"/>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="F157" s="5" t="n"/>
       <c r="G157" s="4">
-        <f>IF(F157="","",IFERROR(VLOOKUP(F157,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F157="","",IFERROR(VLOOKUP(F157,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H157" s="10" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F158" s="5" t="n"/>
       <c r="G158" s="4">
-        <f>IF(F158="","",IFERROR(VLOOKUP(F158,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F158="","",IFERROR(VLOOKUP(F158,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H158" s="10" t="n"/>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F159" s="5" t="n"/>
       <c r="G159" s="4">
-        <f>IF(F159="","",IFERROR(VLOOKUP(F159,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F159="","",IFERROR(VLOOKUP(F159,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H159" s="10" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="F160" s="5" t="n"/>
       <c r="G160" s="4">
-        <f>IF(F160="","",IFERROR(VLOOKUP(F160,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F160="","",IFERROR(VLOOKUP(F160,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H160" s="10" t="n"/>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F161" s="5" t="n"/>
       <c r="G161" s="4">
-        <f>IF(F161="","",IFERROR(VLOOKUP(F161,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F161="","",IFERROR(VLOOKUP(F161,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H161" s="10" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F162" s="5" t="n"/>
       <c r="G162" s="4">
-        <f>IF(F162="","",IFERROR(VLOOKUP(F162,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F162="","",IFERROR(VLOOKUP(F162,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H162" s="10" t="n"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F163" s="5" t="n"/>
       <c r="G163" s="4">
-        <f>IF(F163="","",IFERROR(VLOOKUP(F163,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F163="","",IFERROR(VLOOKUP(F163,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H163" s="10" t="n"/>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F164" s="5" t="n"/>
       <c r="G164" s="4">
-        <f>IF(F164="","",IFERROR(VLOOKUP(F164,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F164="","",IFERROR(VLOOKUP(F164,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H164" s="10" t="n"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="F165" s="5" t="n"/>
       <c r="G165" s="4">
-        <f>IF(F165="","",IFERROR(VLOOKUP(F165,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F165="","",IFERROR(VLOOKUP(F165,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H165" s="10" t="n"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F166" s="5" t="n"/>
       <c r="G166" s="4">
-        <f>IF(F166="","",IFERROR(VLOOKUP(F166,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F166="","",IFERROR(VLOOKUP(F166,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H166" s="10" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F167" s="5" t="n"/>
       <c r="G167" s="4">
-        <f>IF(F167="","",IFERROR(VLOOKUP(F167,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F167="","",IFERROR(VLOOKUP(F167,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H167" s="10" t="n"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F168" s="5" t="n"/>
       <c r="G168" s="4">
-        <f>IF(F168="","",IFERROR(VLOOKUP(F168,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F168="","",IFERROR(VLOOKUP(F168,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H168" s="10" t="n"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="F169" s="5" t="n"/>
       <c r="G169" s="4">
-        <f>IF(F169="","",IFERROR(VLOOKUP(F169,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F169="","",IFERROR(VLOOKUP(F169,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H169" s="10" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F170" s="5" t="n"/>
       <c r="G170" s="4">
-        <f>IF(F170="","",IFERROR(VLOOKUP(F170,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F170="","",IFERROR(VLOOKUP(F170,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H170" s="10" t="n"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F171" s="5" t="n"/>
       <c r="G171" s="4">
-        <f>IF(F171="","",IFERROR(VLOOKUP(F171,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F171="","",IFERROR(VLOOKUP(F171,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H171" s="10" t="n"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F172" s="5" t="n"/>
       <c r="G172" s="4">
-        <f>IF(F172="","",IFERROR(VLOOKUP(F172,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F172="","",IFERROR(VLOOKUP(F172,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H172" s="10" t="n"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F173" s="5" t="n"/>
       <c r="G173" s="4">
-        <f>IF(F173="","",IFERROR(VLOOKUP(F173,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F173="","",IFERROR(VLOOKUP(F173,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H173" s="10" t="n"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="F174" s="5" t="n"/>
       <c r="G174" s="4">
-        <f>IF(F174="","",IFERROR(VLOOKUP(F174,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F174="","",IFERROR(VLOOKUP(F174,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H174" s="10" t="n"/>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="F175" s="5" t="n"/>
       <c r="G175" s="4">
-        <f>IF(F175="","",IFERROR(VLOOKUP(F175,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F175="","",IFERROR(VLOOKUP(F175,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H175" s="10" t="n"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F176" s="5" t="n"/>
       <c r="G176" s="4">
-        <f>IF(F176="","",IFERROR(VLOOKUP(F176,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F176="","",IFERROR(VLOOKUP(F176,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H176" s="10" t="n"/>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F177" s="5" t="n"/>
       <c r="G177" s="4">
-        <f>IF(F177="","",IFERROR(VLOOKUP(F177,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F177="","",IFERROR(VLOOKUP(F177,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H177" s="10" t="n"/>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F178" s="5" t="n"/>
       <c r="G178" s="4">
-        <f>IF(F178="","",IFERROR(VLOOKUP(F178,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F178="","",IFERROR(VLOOKUP(F178,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H178" s="10" t="n"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F179" s="5" t="n"/>
       <c r="G179" s="4">
-        <f>IF(F179="","",IFERROR(VLOOKUP(F179,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F179="","",IFERROR(VLOOKUP(F179,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H179" s="10" t="n"/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F180" s="5" t="n"/>
       <c r="G180" s="4">
-        <f>IF(F180="","",IFERROR(VLOOKUP(F180,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F180="","",IFERROR(VLOOKUP(F180,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H180" s="10" t="n"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F181" s="5" t="n"/>
       <c r="G181" s="4">
-        <f>IF(F181="","",IFERROR(VLOOKUP(F181,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F181="","",IFERROR(VLOOKUP(F181,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H181" s="10" t="n"/>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F182" s="5" t="n"/>
       <c r="G182" s="4">
-        <f>IF(F182="","",IFERROR(VLOOKUP(F182,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F182="","",IFERROR(VLOOKUP(F182,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H182" s="10" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="F183" s="5" t="n"/>
       <c r="G183" s="4">
-        <f>IF(F183="","",IFERROR(VLOOKUP(F183,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F183="","",IFERROR(VLOOKUP(F183,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H183" s="10" t="n"/>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F184" s="5" t="n"/>
       <c r="G184" s="4">
-        <f>IF(F184="","",IFERROR(VLOOKUP(F184,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F184="","",IFERROR(VLOOKUP(F184,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H184" s="10" t="n"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="F185" s="5" t="n"/>
       <c r="G185" s="4">
-        <f>IF(F185="","",IFERROR(VLOOKUP(F185,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F185="","",IFERROR(VLOOKUP(F185,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H185" s="10" t="n"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="F186" s="5" t="n"/>
       <c r="G186" s="4">
-        <f>IF(F186="","",IFERROR(VLOOKUP(F186,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F186="","",IFERROR(VLOOKUP(F186,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H186" s="10" t="n"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="F187" s="5" t="n"/>
       <c r="G187" s="4">
-        <f>IF(F187="","",IFERROR(VLOOKUP(F187,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F187="","",IFERROR(VLOOKUP(F187,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H187" s="10" t="n"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F188" s="5" t="n"/>
       <c r="G188" s="4">
-        <f>IF(F188="","",IFERROR(VLOOKUP(F188,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F188="","",IFERROR(VLOOKUP(F188,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H188" s="10" t="n"/>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="F189" s="5" t="n"/>
       <c r="G189" s="4">
-        <f>IF(F189="","",IFERROR(VLOOKUP(F189,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F189="","",IFERROR(VLOOKUP(F189,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H189" s="10" t="n"/>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="F190" s="5" t="n"/>
       <c r="G190" s="4">
-        <f>IF(F190="","",IFERROR(VLOOKUP(F190,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F190="","",IFERROR(VLOOKUP(F190,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H190" s="10" t="n"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F191" s="5" t="n"/>
       <c r="G191" s="4">
-        <f>IF(F191="","",IFERROR(VLOOKUP(F191,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F191="","",IFERROR(VLOOKUP(F191,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H191" s="10" t="n"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F192" s="5" t="n"/>
       <c r="G192" s="4">
-        <f>IF(F192="","",IFERROR(VLOOKUP(F192,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F192="","",IFERROR(VLOOKUP(F192,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H192" s="10" t="n"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F193" s="5" t="n"/>
       <c r="G193" s="4">
-        <f>IF(F193="","",IFERROR(VLOOKUP(F193,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F193="","",IFERROR(VLOOKUP(F193,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H193" s="10" t="n"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F194" s="5" t="n"/>
       <c r="G194" s="4">
-        <f>IF(F194="","",IFERROR(VLOOKUP(F194,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F194="","",IFERROR(VLOOKUP(F194,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H194" s="10" t="n"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="F195" s="5" t="n"/>
       <c r="G195" s="4">
-        <f>IF(F195="","",IFERROR(VLOOKUP(F195,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F195="","",IFERROR(VLOOKUP(F195,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H195" s="10" t="n"/>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F196" s="5" t="n"/>
       <c r="G196" s="4">
-        <f>IF(F196="","",IFERROR(VLOOKUP(F196,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F196="","",IFERROR(VLOOKUP(F196,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H196" s="10" t="n"/>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="F197" s="5" t="n"/>
       <c r="G197" s="4">
-        <f>IF(F197="","",IFERROR(VLOOKUP(F197,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F197="","",IFERROR(VLOOKUP(F197,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H197" s="10" t="n"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="F198" s="5" t="n"/>
       <c r="G198" s="4">
-        <f>IF(F198="","",IFERROR(VLOOKUP(F198,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F198="","",IFERROR(VLOOKUP(F198,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H198" s="10" t="n"/>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F199" s="5" t="n"/>
       <c r="G199" s="4">
-        <f>IF(F199="","",IFERROR(VLOOKUP(F199,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F199="","",IFERROR(VLOOKUP(F199,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H199" s="10" t="n"/>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F200" s="5" t="n"/>
       <c r="G200" s="4">
-        <f>IF(F200="","",IFERROR(VLOOKUP(F200,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F200="","",IFERROR(VLOOKUP(F200,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H200" s="10" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F201" s="5" t="n"/>
       <c r="G201" s="4">
-        <f>IF(F201="","",IFERROR(VLOOKUP(F201,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F201="","",IFERROR(VLOOKUP(F201,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H201" s="10" t="n"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="F202" s="5" t="n"/>
       <c r="G202" s="4">
-        <f>IF(F202="","",IFERROR(VLOOKUP(F202,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F202="","",IFERROR(VLOOKUP(F202,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H202" s="10" t="n"/>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="F203" s="5" t="n"/>
       <c r="G203" s="4">
-        <f>IF(F203="","",IFERROR(VLOOKUP(F203,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F203="","",IFERROR(VLOOKUP(F203,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H203" s="10" t="n"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="F204" s="5" t="n"/>
       <c r="G204" s="4">
-        <f>IF(F204="","",IFERROR(VLOOKUP(F204,Справочник!$A$18:$B$26,2,FALSE),"Выберите реакцию из списка"))</f>
+        <f>IF(F204="","",IFERROR(VLOOKUP(F204,Справочник!$A$19:$B$27,2,FALSE),"Выберите реакцию из списка"))</f>
         <v/>
       </c>
       <c r="H204" s="10" t="n"/>
@@ -5053,7 +5053,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="F5:F204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Справочник!$A$18:$A$26</formula1>
+      <formula1>Справочник!$A$19:$A$27</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5067,7 +5067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Зафиксируйте в реестре передачи, какая документация требуется договором и что уже передано. Если без неё оплата по договору не наступает — сначала закройте передачу документации, затем вернитесь к шагу 6.</t>
+          <t>Зафиксируйте в реестре передачи, какая документация требуется договором и что уже передано. Если без неё оплата по договору не наступает — сначала закройте передачу документации, затем пройдите проверку G перед шагом 6.</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Оформите акты (файлы 04–07), проверьте (09), передайте с доказательством и закройте замечания (10), затем шаг 6.</t>
+          <t>Оформите акты (файлы 04–07), проверьте (09), передайте с доказательством и закройте замечания (10), затем проверка G (файл 03). Задолженность до неё не фиксируйте.</t>
         </is>
       </c>
     </row>
@@ -5258,118 +5258,122 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Маршрут начните на следующий день после срока. До этого документы можно готовить по ситуации Г (шаги 2–5).</t>
+          <t>Маршрут задолженности (шаги 6–12) начните не раньше следующего дня после срока. До этого документы можно готовить и сдавать по ситуации Г (шаги 2–4).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>ПЕРЕДАЧА</t>
+          <t>ПОДПИСЬ</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>СИТУАЦИЯ Е, ШАГ 4: подтвердить передачу</t>
+          <t>СИТУАЦИЯ Е: приёмка не подтверждена</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Передайте документы способом, который можно доказать, и внесите передачу в реестр (файлы 10, 08).</t>
+          <t>Приёмка не подтверждена, поэтому долг не фиксируйте и претензию не готовьте. Проверьте по договору срок и порядок приёмки; направьте заказчику запрос подписать акт или прислать мотивированный отказ и повторно предъявите документы (файл 10, раздел Б); каждую отправку внесите в реестр передачи (файл 08). Если считаете работы принятыми по акту, подписанному только вами, — граница B4.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>ЗАМЕЧАНИЯ</t>
+          <t>ПЕРЕДАЧА</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>СИТУАЦИЯ Д, ШАГ 5: закрыть замечания</t>
+          <t>СИТУАЦИЯ Г, ШАГ 4: подтвердить передачу</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Разберите замечания по файлу 10, раздел Б; ведите реестр замечаний (файл 08).</t>
+          <t>Передайте документы способом, который можно доказать, и внесите передачу в реестр (файлы 10, 08), затем проверка G (файл 03).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>СВЕРКА</t>
+          <t>ЗАМЕЧАНИЯ</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>СИТУАЦИЯ Б, ШАГ 6: подтвердить сумму</t>
+          <t>СИТУАЦИЯ Д, ШАГ 5: закрыть замечания</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Заполните реестр взаиморасчётов (файл 08) и предложите заказчику акт сверки; шаги 2–5 не нужны.</t>
+          <t>Разберите замечания по файлу 10, раздел Б; ведите реестр замечаний (файл 08), затем проверка G (файл 03).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>СВЕРКА</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>СИТУАЦИЯ Б, ШАГ 6: подтвердить сумму</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Заполните реестр взаиморасчётов (файл 08) и предложите заказчику акт сверки; шаги 2–5 не нужны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>МОЖНО ИДТИ ПО S1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Ситуация А: шаги 6–12. Зафиксируйте долг и дату начала просрочки, затем переговоры (файл 11).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Реакция заказчика</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Следующий шаг</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Оплатил полностью</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Внесите оплату в реестр взаиморасчётов (файл 08). Маршрут завершён.</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Оплатил частично</t>
+          <t>Оплатил полностью</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Внесите оплату в реестр взаиморасчётов (08) и в расчёт процентов (14). По остатку — шаги 9–12.</t>
+          <t>Внесите оплату в реестр взаиморасчётов (файл 08). Маршрут завершён.</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -5377,12 +5381,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Обещал оплатить в названную дату</t>
+          <t>Оплатил частично</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Контролируйте дату. При срыве — сразу шаги 9–10, без повторного письма.</t>
+          <t>Внесите оплату в реестр взаиморасчётов (08) и в расчёт процентов (14). По остатку — шаги 9–12.</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -5390,12 +5394,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Предложил график или перенос</t>
+          <t>Обещал оплатить в названную дату</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Только двустороннее соглашение (файл 11, раздел Б). Гарантийное письмо соглашение не заменяет.</t>
+          <t>Контролируйте дату. При срыве — сразу шаги 9–10, без повторного письма.</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -5403,12 +5407,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Молчание после срока</t>
+          <t>Предложил график или перенос</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Если это была претензия и срок ожидания истёк — шаг 12 (файл 15). Если уведомление — шаги 9–10.</t>
+          <t>Только двустороннее соглашение (файл 11, раздел Б). Гарантийное письмо соглашение не заменяет.</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -5416,12 +5420,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Отказ без мотивов</t>
+          <t>Молчание после срока</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Если претензия ещё не направлена — шаг 10; если направлена и срок ожидания истёк — шаг 12.</t>
+          <t>Если это была претензия и срок ожидания истёк — шаг 12 (файл 15). Если уведомление — шаги 9–10.</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -5429,12 +5433,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Отказ с мотивами: объём, качество, подпись</t>
+          <t>Отказ без мотивов</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Граница B4: профессиональная оценка. Опись материалов — файл 15, раздел В.</t>
+          <t>Если претензия ещё не направлена — шаг 10; если направлена и срок ожидания истёк — шаг 12.</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -5442,12 +5446,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Встречное требование, зачёт, удержание, неустойка</t>
+          <t>Отказ с мотивами: объём, качество, подпись</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Граница B2: спорную часть — специалисту; бесспорную — дальше по маршруту.</t>
+          <t>Граница B4: профессиональная оценка. Опись материалов — файл 15, раздел В.</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -5455,15 +5459,28 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Встречное требование, зачёт, удержание, неустойка</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Граница B2: спорную часть — специалисту; бесспорную — дальше по маршруту.</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>Признаки банкротства</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Граница B3: остановите маршрут и немедленно обратитесь к специалисту по банкротству.</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/02-pervichnaya-proverka-i-kontrol.xlsx
@@ -824,7 +824,7 @@
     <row r="27" ht="45" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Последний день срока оплаты (по договору или двустороннему соглашению; если он пришёлся на нерабочий день — ближайший следующий рабочий день, ст. 193 ГК РФ)</t>
+          <t>Последний день срока оплаты (по договору или двустороннему соглашению; если он пришёлся на нерабочий день — ближайший следующий рабочий день, ст. 193 ГК РФ). Если актов несколько и сроки оплаты по ним разные, заполните срок по каждому акту в файле 08, лист «Долг по актам»: эта строка тогда служит для самого раннего акта</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
@@ -832,7 +832,7 @@
     <row r="28" ht="45" customHeight="1">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Первый день просрочки (перенесите в файл 14, лист «Ввод»)</t>
+          <t>Первый день просрочки (по каждому акту он свой: файл 08, лист «Долг по актам», оттуда — в файл 14, лист «Акты», вместе с долгом на первый день просрочки)</t>
         </is>
       </c>
       <c r="C28" s="9">
